--- a/Result/profitability/1304.xlsx
+++ b/Result/profitability/1304.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.71</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4625</v>
+        <v>-0.4075</v>
       </c>
       <c r="N2" t="n">
-        <v>4.057499999999999</v>
+        <v>5.47875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -684,13 +684,13 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.75</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2925</v>
+        <v>-0.215</v>
       </c>
       <c r="N3" t="n">
-        <v>5.51875</v>
+        <v>6.883749999999999</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.29</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1575</v>
+        <v>-0.105</v>
       </c>
       <c r="N4" t="n">
-        <v>6.28375</v>
+        <v>7.555</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.64</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.28875</v>
+        <v>-0.20875</v>
       </c>
       <c r="N5" t="n">
-        <v>2.94125</v>
+        <v>4.436249999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.46</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.13</v>
+        <v>-0.09500000000000003</v>
       </c>
       <c r="N6" t="n">
-        <v>4.768750000000001</v>
+        <v>6.282500000000001</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.92</v>
       </c>
       <c r="M7" t="n">
-        <v>0.04125000000000004</v>
+        <v>0.11375</v>
       </c>
       <c r="N7" t="n">
-        <v>6.5925</v>
+        <v>7.645</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.04</v>
       </c>
       <c r="M8" t="n">
-        <v>0.265</v>
+        <v>0.295</v>
       </c>
       <c r="N8" t="n">
-        <v>8.032499999999999</v>
+        <v>9.395</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.36</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3612500000000001</v>
+        <v>0.36125</v>
       </c>
       <c r="N9" t="n">
         <v>9.4975</v>
@@ -1899,7 +1899,7 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4425000000000001</v>
+        <v>0.4424999999999999</v>
       </c>
       <c r="N12" t="n">
         <v>10.39125</v>
@@ -2026,7 +2026,7 @@
         <v>1.36</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8174999999999999</v>
+        <v>0.8175</v>
       </c>
       <c r="N13" t="n">
         <v>16.19625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>11014</v>
+      </c>
+      <c r="D75" t="n">
+        <v>9498</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1515</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.76</v>
+      </c>
+      <c r="G75" t="n">
+        <v>396</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.60%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-917</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-521</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-179</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.5725</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4.27875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.5853658536585366</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>3.811188811188812</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7901234567901234</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>6.644444444444444</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
